--- a/jogos_2025-11-08.xlsx
+++ b/jogos_2025-11-08.xlsx
@@ -669,13 +669,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>4.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -708,10 +708,10 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA2" t="n">
         <v>0</v>
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Suzhou Dongwu</t>
+          <t>Yanbian Longding</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Heilongjiang Lava Spring</t>
+          <t>Nanjing City</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Guangzhou E-Power</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Chongqing Tongliang Long</t>
+          <t>Nantong Zhiyun</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Shaanxi Union</t>
+          <t>Suzhou Dongwu</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Guangxi Baoyun</t>
+          <t>Heilongjiang Lava Spring</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Hebei Kungfu</t>
+          <t>Shaanxi Union</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Dalian Huayi</t>
+          <t>Guangxi Baoyun</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Yanbian Longding</t>
+          <t>Hebei Kungfu</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Nanjing City</t>
+          <t>Dalian Huayi</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Shenyang Urban</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Dongguan United</t>
+          <t>Chongqing Tongliang Long</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shenyang Urban</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qingdao Red Lions</t>
+          <t>Dongguan United</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Guangzhou E-Power</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nantong Zhiyun</t>
+          <t>Qingdao Red Lions</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1959,13 +1959,13 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O12" t="n">
         <v>0</v>
@@ -1998,10 +1998,10 @@
         <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -2578,12 +2578,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2836,12 +2836,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2965,12 +2965,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -3223,12 +3223,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hoang Anh Gia Lai</t>
+          <t>Bahardar</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>FLC Thanh Hoa</t>
+          <t>Kedus Giorgis</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -3342,7 +3342,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3352,12 +3352,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Bahardar</t>
+          <t>Lokomotiv Sofia 1929</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kedus Giorgis</t>
+          <t>Botev Vratsa</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -3378,13 +3378,13 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O23" t="n">
         <v>0</v>
@@ -3417,10 +3417,10 @@
         <v>0</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA23" t="n">
         <v>0</v>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Lokomotiv Sofia 1929</t>
+          <t>Hoang Anh Gia Lai</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Botev Vratsa</t>
+          <t>FLC Thanh Hoa</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -3507,13 +3507,13 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N24" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -3546,10 +3546,10 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z24" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA24" t="n">
         <v>0</v>
@@ -3610,12 +3610,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Tallinna Kalev</t>
+          <t>Tammeka</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kuressaare</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -3729,22 +3729,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Tammeka</t>
+          <t>Bandırmaspor</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Boluspor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -3868,12 +3868,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Harju Jalgpallikool</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Paide</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -3894,13 +3894,13 @@
         </is>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>6.35</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3933,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AC27" t="n">
         <v>0</v>
@@ -3987,22 +3987,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Sivasspor</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Manisa BBSK</t>
+          <t>Tallinna FC Flora</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -4116,22 +4116,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bandırmaspor</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Boluspor</t>
+          <t>Paide</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -4245,22 +4245,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Harju Jalgpallikool</t>
+          <t>Sivasspor</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Manisa BBSK</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -4281,13 +4281,13 @@
         </is>
       </c>
       <c r="L30" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="M30" t="n">
-        <v>6.35</v>
+        <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
         <v>0</v>
@@ -4320,16 +4320,16 @@
         <v>0</v>
       </c>
       <c r="Y30" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="Z30" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA30" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="AB30" t="n">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="AC30" t="n">
         <v>0</v>
@@ -4384,12 +4384,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Tallinna Kalev</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallinna FC Flora</t>
+          <t>Kuressaare</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Vietnam V.League 1</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -4513,12 +4513,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Posta Rangers</t>
+          <t>Pho Hien</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>TransMara Sugar</t>
+          <t>Viettel</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -4632,7 +4632,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Vietnam V.League 1</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Pho Hien</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viettel</t>
+          <t>Kanchanaburi</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -4771,12 +4771,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sukhothai</t>
+          <t>Posta Rangers</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kanchanaburi</t>
+          <t>TransMara Sugar</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -5184,13 +5184,13 @@
         </is>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>3.91</v>
       </c>
       <c r="O37" t="n">
         <v>0</v>
@@ -5223,10 +5223,10 @@
         <v>0</v>
       </c>
       <c r="Y37" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="Z37" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AA37" t="n">
         <v>0</v>
@@ -5535,7 +5535,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -5545,12 +5545,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Arsenal Women</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Darmstadt 98</t>
+          <t>Chelsea Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>England FA Women's Super League</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -5674,12 +5674,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Schalke 04</t>
+          <t>Manchester United Women</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Elversberg</t>
+          <t>Aston Villa Ladies</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -5793,22 +5793,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Piteå Women</t>
+          <t>Schalke 04</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rosengard Women</t>
+          <t>Elversberg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Thailand Thai League T1</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -6061,12 +6061,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Uthai Thani</t>
+          <t>Arsenal Tula</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Muang Thong United</t>
+          <t>Chayka</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -6180,7 +6180,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Indonesia Liga 1</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Arsenal Tula</t>
+          <t>Persis Solo</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Chayka</t>
+          <t>PSIM Yogyakarta</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -6309,22 +6309,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Arsenal Women</t>
+          <t>Piteå Women</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Chelsea Women</t>
+          <t>Rosengard Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -6438,7 +6438,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Thailand Thai League T1</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -6448,12 +6448,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Bandari</t>
+          <t>Uthai Thani</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sofapaka</t>
+          <t>Muang Thong United</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -6567,7 +6567,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FYR Macedonia First Football League</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -6577,12 +6577,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>FK Bashkimi Kumanovo</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rabotnički</t>
+          <t>Darmstadt 98</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -6696,7 +6696,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>England FA Women's Super League</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Manchester United Women</t>
+          <t>Bandari</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Aston Villa Ladies</t>
+          <t>Sofapaka</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Indonesia Liga 1</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Persis Solo</t>
+          <t>FK Bashkimi Kumanovo</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>PSIM Yogyakarta</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -6954,7 +6954,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -6964,12 +6964,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hull City</t>
+          <t>Crewe Alexandra</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Portsmouth</t>
+          <t>Shrewsbury Town</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -6990,13 +6990,13 @@
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="M51" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="O51" t="n">
         <v>0</v>
@@ -7029,10 +7029,10 @@
         <v>0</v>
       </c>
       <c r="Y51" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z51" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA51" t="n">
         <v>0</v>
@@ -7083,7 +7083,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -7093,12 +7093,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Tottenham Hotspur</t>
+          <t>Millwall</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -7119,13 +7119,13 @@
         </is>
       </c>
       <c r="L52" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M52" t="n">
-        <v>3.92</v>
+        <v>0</v>
       </c>
       <c r="N52" t="n">
-        <v>2.49</v>
+        <v>0</v>
       </c>
       <c r="O52" t="n">
         <v>0</v>
@@ -7158,10 +7158,10 @@
         <v>0</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="Z52" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="AA52" t="n">
         <v>0</v>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Colchester United</t>
+          <t>Tottenham Hotspur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bromley</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -7377,13 +7377,13 @@
         </is>
       </c>
       <c r="L54" t="n">
-        <v>2.25</v>
+        <v>2.45</v>
       </c>
       <c r="M54" t="n">
-        <v>3.55</v>
+        <v>3.92</v>
       </c>
       <c r="N54" t="n">
-        <v>2.85</v>
+        <v>2.49</v>
       </c>
       <c r="O54" t="n">
         <v>0</v>
@@ -7416,10 +7416,10 @@
         <v>0</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="Z54" t="n">
-        <v>2.02</v>
+        <v>2.37</v>
       </c>
       <c r="AA54" t="n">
         <v>0</v>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -7480,12 +7480,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wycombe Wanderers</t>
+          <t>Hull City</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Leyton Orient</t>
+          <t>Portsmouth</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -7506,13 +7506,13 @@
         </is>
       </c>
       <c r="L55" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="M55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N55" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="O55" t="n">
         <v>0</v>
@@ -7545,10 +7545,10 @@
         <v>0</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="Z55" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AA55" t="n">
         <v>0</v>
@@ -7609,12 +7609,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Crewe Alexandra</t>
+          <t>Colchester United</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Shrewsbury Town</t>
+          <t>Bromley</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -7635,13 +7635,13 @@
         </is>
       </c>
       <c r="L56" t="n">
-        <v>1.97</v>
+        <v>2.25</v>
       </c>
       <c r="M56" t="n">
-        <v>3.15</v>
+        <v>3.55</v>
       </c>
       <c r="N56" t="n">
-        <v>3.9</v>
+        <v>2.85</v>
       </c>
       <c r="O56" t="n">
         <v>0</v>
@@ -7674,10 +7674,10 @@
         <v>0</v>
       </c>
       <c r="Y56" t="n">
-        <v>2.2</v>
+        <v>1.7</v>
       </c>
       <c r="Z56" t="n">
-        <v>1.6</v>
+        <v>2.02</v>
       </c>
       <c r="AA56" t="n">
         <v>0</v>
@@ -7728,7 +7728,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Millwall</t>
+          <t>Petrolul 52</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Oţelul Galaţi</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -7764,13 +7764,13 @@
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="M57" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="N57" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="O57" t="n">
         <v>0</v>
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Petrolul 52</t>
+          <t>Wycombe Wanderers</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Oţelul Galaţi</t>
+          <t>Leyton Orient</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -8022,13 +8022,13 @@
         </is>
       </c>
       <c r="L59" t="n">
-        <v>2.4</v>
+        <v>1.75</v>
       </c>
       <c r="M59" t="n">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="N59" t="n">
-        <v>3.02</v>
+        <v>4.2</v>
       </c>
       <c r="O59" t="n">
         <v>0</v>
@@ -8061,10 +8061,10 @@
         <v>0</v>
       </c>
       <c r="Y59" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="Z59" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AA59" t="n">
         <v>0</v>
@@ -8115,7 +8115,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -8125,12 +8125,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Levski Sofia</t>
+          <t>Girona FC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>CSKA Sofia</t>
+          <t>Deportivo Alavés</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -8151,13 +8151,13 @@
         </is>
       </c>
       <c r="L60" t="n">
-        <v>2</v>
+        <v>2.35</v>
       </c>
       <c r="M60" t="n">
-        <v>3.3</v>
+        <v>3.17</v>
       </c>
       <c r="N60" t="n">
-        <v>4.05</v>
+        <v>3.2</v>
       </c>
       <c r="O60" t="n">
         <v>0</v>
@@ -8190,10 +8190,10 @@
         <v>0</v>
       </c>
       <c r="Y60" t="n">
-        <v>2.35</v>
+        <v>2.37</v>
       </c>
       <c r="Z60" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="AA60" t="n">
         <v>0</v>
@@ -8244,22 +8244,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Brommapojkarna W</t>
+          <t>Twente W</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AIK Women</t>
+          <t>Feyenoord W</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -8373,22 +8373,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Djurgården W</t>
+          <t>Schweinfurt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Häcken W</t>
+          <t>Hoffenheim II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -8502,7 +8502,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -8512,12 +8512,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Levski Sofia</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rot-Weiss Essen</t>
+          <t>CSKA Sofia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -8538,13 +8538,13 @@
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M63" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N63" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="O63" t="n">
         <v>0</v>
@@ -8577,10 +8577,10 @@
         <v>0</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AA63" t="n">
         <v>0</v>
@@ -8631,22 +8631,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Dainava</t>
+          <t>Ethiopian Medhin</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Arba Minch Kenema</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -8760,7 +8760,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -8770,12 +8770,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Hegelmann Litauen</t>
+          <t>Trondheims-Ørn</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Sūduva</t>
+          <t>Vålerenga Women</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -8889,7 +8889,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Kenya Kenyan Premier League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Ajax W</t>
+          <t>Leopards</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>PSV W</t>
+          <t>Murang'a SEAL</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -9018,7 +9018,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -9028,12 +9028,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Girona FC</t>
+          <t>Ulm</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Deportivo Alavés</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -9054,13 +9054,13 @@
         </is>
       </c>
       <c r="L67" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M67" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="N67" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="O67" t="n">
         <v>0</v>
@@ -9093,10 +9093,10 @@
         <v>0</v>
       </c>
       <c r="Y67" t="n">
-        <v>2.37</v>
+        <v>0</v>
       </c>
       <c r="Z67" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA67" t="n">
         <v>0</v>
@@ -9147,22 +9147,22 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Energie Cottbus</t>
+          <t>Hegelmann Litauen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Osnabrück</t>
+          <t>Sūduva</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -9276,22 +9276,22 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Panevėžys</t>
+          <t>Rodina Moskva</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Žalgiris</t>
+          <t>Neftekhimik</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -9405,7 +9405,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Netherlands Eredivisie Women</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Schweinfurt</t>
+          <t>Ajax W</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Hoffenheim II</t>
+          <t>PSV W</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -9544,12 +9544,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Real Sociedad II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Leganés</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -9663,22 +9663,22 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Sakaryaspor</t>
+          <t>Sarpsborg 08</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Serik Belediyespor</t>
+          <t>Fredrikstad</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -9792,7 +9792,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie Women</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -9802,12 +9802,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Twente W</t>
+          <t>Shire Endaselassie</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Feyenoord W</t>
+          <t>Sidama Bunna</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -9921,22 +9921,22 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Real Sociedad II</t>
+          <t>Røa Women</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Leganés</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -10050,22 +10050,22 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Verl</t>
+          <t>Panevėžys</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Erzgebirge Aue</t>
+          <t>Žalgiris</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -10179,22 +10179,22 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Verl</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Džiugas Telšiai</t>
+          <t>Erzgebirge Aue</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -10308,22 +10308,22 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Dubrava Zagreb</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dugopolje</t>
+          <t>Kolbotn</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Lillestrøm W</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolbotn</t>
+          <t>Lyn W</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -10566,22 +10566,22 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Trondheims-Ørn</t>
+          <t>CD Teruel</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Vålerenga Women</t>
+          <t>FC Cartagena</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -10705,12 +10705,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Hanácká</t>
+          <t>Ingolstadt</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Baník Ostrava U21</t>
+          <t>Rot-Weiss Essen</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -10824,7 +10824,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -10834,12 +10834,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Shire Endaselassie</t>
+          <t>Energie Cottbus</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sidama Bunna</t>
+          <t>Osnabrück</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -10953,22 +10953,22 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Ethiopian Medhin</t>
+          <t>Brommapojkarna W</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Arba Minch Kenema</t>
+          <t>AIK Women</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -11082,22 +11082,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>CD Teruel</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>FC Cartagena</t>
+          <t>Džiugas Telšiai</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -11211,22 +11211,22 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Kenya Kenyan Premier League</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Leopards</t>
+          <t>Stabæk Women</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Murang'a SEAL</t>
+          <t>SK Brann Kvinner W</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -11340,22 +11340,22 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Lillestrøm W</t>
+          <t>Sakaryaspor</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lyn W</t>
+          <t>Serik Belediyespor</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -11469,7 +11469,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -11479,12 +11479,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Sarpsborg 08</t>
+          <t>Dainava</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Fredrikstad</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -11598,7 +11598,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -11608,12 +11608,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Stabæk Women</t>
+          <t>Kauno Žalgiris</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>SK Brann Kvinner W</t>
+          <t>Banga</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -11727,22 +11727,22 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Røa Women</t>
+          <t>Hanácká</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Baník Ostrava U21</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -11856,22 +11856,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kauno Žalgiris</t>
+          <t>Dubrava Zagreb</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Banga</t>
+          <t>Dugopolje</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -11985,22 +11985,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Rodina Moskva</t>
+          <t>Djurgården W</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Neftekhimik</t>
+          <t>Häcken W</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Wisła Kraków</t>
+          <t>Arzignano Valchiampo</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Polonia Warszawa</t>
+          <t>Pergolettese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -12243,7 +12243,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CS Sfaxien</t>
+          <t>Renate</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Marsa</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -12372,7 +12372,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -12382,12 +12382,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Dolomiti Bellunesi</t>
+          <t>Schwarz-Weiß Bregenz</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cittadella</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -12408,13 +12408,13 @@
         </is>
       </c>
       <c r="L93" t="n">
-        <v>3.93</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
         <v>0</v>
@@ -12447,10 +12447,10 @@
         <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1.57</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
         <v>0</v>
@@ -12501,7 +12501,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -12511,12 +12511,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Monastir</t>
+          <t>Wisła Kraków</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Kairouan</t>
+          <t>Polonia Warszawa</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -12630,7 +12630,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -12640,12 +12640,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Schwarz-Weiß Bregenz</t>
+          <t>Gabès</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>AS Slimane</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -12759,7 +12759,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -12769,12 +12769,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Arzignano Valchiampo</t>
+          <t>Monastir</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Pergolettese</t>
+          <t>Kairouan</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -12888,7 +12888,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -12898,12 +12898,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CA Bizertin</t>
+          <t>Dolomiti Bellunesi</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Etoile du Sahel</t>
+          <t>Cittadella</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -12924,13 +12924,13 @@
         </is>
       </c>
       <c r="L97" t="n">
-        <v>0</v>
+        <v>3.93</v>
       </c>
       <c r="M97" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="O97" t="n">
         <v>0</v>
@@ -12963,10 +12963,10 @@
         <v>0</v>
       </c>
       <c r="Y97" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="Z97" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AA97" t="n">
         <v>0</v>
@@ -13017,7 +13017,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -13027,12 +13027,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>CS Sfaxien</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Sturm Graz II</t>
+          <t>Marsa</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -13146,7 +13146,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -13156,12 +13156,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Atalanta II</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>SSC Giugliano</t>
+          <t>Pineto</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -13285,12 +13285,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Renate</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -13404,7 +13404,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -13414,12 +13414,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Atalanta II</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Pineto</t>
+          <t>SSC Giugliano</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -13533,7 +13533,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -13543,12 +13543,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Gabès</t>
+          <t>Trapani 1905</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>AS Slimane</t>
+          <t>Picerno</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -13662,7 +13662,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -13672,12 +13672,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>CA Bizertin</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Etoile du Sahel</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -13801,12 +13801,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Trapani 1905</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Picerno</t>
+          <t>Sturm Graz II</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -13930,12 +13930,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Zalaegerszegi TE</t>
+          <t>Lechia Gdańsk</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Diósgyőr</t>
+          <t>Widzew Łódź</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -14049,7 +14049,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -14059,12 +14059,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lechia Gdańsk</t>
+          <t>Zalaegerszegi TE</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Widzew Łódź</t>
+          <t>Diósgyőr</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -14307,7 +14307,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -14317,12 +14317,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Frosinone</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Modena</t>
+          <t>Alanyaspor</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -14436,22 +14436,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Südtirol</t>
+          <t>Qizilqum</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Carrarese</t>
+          <t>Andijan</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -14565,7 +14565,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -14575,12 +14575,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Portimonense</t>
+          <t>KAMAZ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>UD Oliveirense</t>
+          <t>Volga Ulyanovsk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -14694,7 +14694,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Sweden Damallsvenskan</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -14704,12 +14704,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sandviken</t>
+          <t>Norrköping W</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Östersunds FK</t>
+          <t>Malmö FF W</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -14823,22 +14823,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Xorazm</t>
+          <t>Frosinone</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Sogdiana</t>
+          <t>Modena</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -14952,22 +14952,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Sweden Damallsvenskan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Norrköping W</t>
+          <t>Mantova</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Malmö FF W</t>
+          <t>Calcio Padova</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -15081,7 +15081,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -15091,12 +15091,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Empoli</t>
+          <t>Portimonense</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Catanzaro</t>
+          <t>UD Oliveirense</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -15210,7 +15210,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -15220,12 +15220,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Reggiana</t>
+          <t>Lokomotiva Zagreb</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Virtus Entella</t>
+          <t>Slaven Koprivnica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -15339,22 +15339,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Lyn</t>
+          <t>Südtirol</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Start</t>
+          <t>Carrarese</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -15468,22 +15468,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Qizilqum</t>
+          <t>Reggiana</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Andijan</t>
+          <t>Virtus Entella</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -15597,22 +15597,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kalmar</t>
+          <t>Como</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Falkenberg</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -15633,13 +15633,13 @@
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="M118" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="N118" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="O118" t="n">
         <v>0</v>
@@ -15672,10 +15672,10 @@
         <v>0</v>
       </c>
       <c r="Y118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z118" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA118" t="n">
         <v>0</v>
@@ -15726,22 +15726,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zlín</t>
+          <t>Hødd</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Bohemians 1905</t>
+          <t>Aalesund</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -15855,7 +15855,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -15865,12 +15865,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Oddevold</t>
+          <t>Lillestrøm</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Helsingborg</t>
+          <t>Stabæk</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -15984,22 +15984,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Dukla Praha</t>
+          <t>Mjøndalen</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Egersund</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -16113,22 +16113,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Brage</t>
+          <t>Empoli</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Landskrona</t>
+          <t>Catanzaro</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -16252,12 +16252,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Trelleborg</t>
+          <t>Skeid</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Örebro</t>
+          <t>Odd</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -16371,7 +16371,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -16381,12 +16381,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>KAMAZ</t>
+          <t>Lecce</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Volga Ulyanovsk</t>
+          <t>Hellas Verona</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -16407,13 +16407,13 @@
         </is>
       </c>
       <c r="L124" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M124" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="N124" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O124" t="n">
         <v>0</v>
@@ -16440,16 +16440,16 @@
         <v>0</v>
       </c>
       <c r="W124" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="X124" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Y124" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Z124" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AA124" t="n">
         <v>0</v>
@@ -16500,22 +16500,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Åsane</t>
+          <t>Akritas</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Kongsvinger</t>
+          <t>Olympiakos</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -16629,7 +16629,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -16639,12 +16639,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Utsikten</t>
+          <t>Xorazm</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Umeå</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -16768,12 +16768,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sogndal</t>
+          <t>Moss</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Ranheim</t>
+          <t>Raufoss</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -16897,12 +16897,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Mjøndalen</t>
+          <t>Lyn</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Egersund</t>
+          <t>Start</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -17016,7 +17016,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -17026,12 +17026,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Moss</t>
+          <t>Trelleborg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Raufoss</t>
+          <t>Örebro</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -17145,22 +17145,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>GIF Sundsvall</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Slovácko</t>
+          <t>Örgryte</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -17274,22 +17274,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Lecce</t>
+          <t>Sandviken</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Hellas Verona</t>
+          <t>Östersunds FK</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -17310,13 +17310,13 @@
         </is>
       </c>
       <c r="L131" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M131" t="n">
-        <v>2.85</v>
+        <v>0</v>
       </c>
       <c r="N131" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O131" t="n">
         <v>0</v>
@@ -17343,16 +17343,16 @@
         <v>0</v>
       </c>
       <c r="W131" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="X131" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Y131" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Z131" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="AA131" t="n">
         <v>0</v>
@@ -17403,7 +17403,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -17413,12 +17413,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Hødd</t>
+          <t>Västerås SK</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Aalesund</t>
+          <t>Varberg</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -17532,22 +17532,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Lokomotiva Zagreb</t>
+          <t>Utsikten</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Slaven Koprivnica</t>
+          <t>Umeå</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -17661,7 +17661,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -17671,12 +17671,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Skeid</t>
+          <t>Oddevold</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Odd</t>
+          <t>Helsingborg</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -17800,12 +17800,12 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Dukla Praha</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Alanyaspor</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -17919,7 +17919,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -17929,12 +17929,12 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Como</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Slovácko</t>
         </is>
       </c>
       <c r="G136" t="n">
@@ -17955,13 +17955,13 @@
         </is>
       </c>
       <c r="L136" t="n">
-        <v>1.52</v>
+        <v>0</v>
       </c>
       <c r="M136" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="N136" t="n">
-        <v>6.1</v>
+        <v>0</v>
       </c>
       <c r="O136" t="n">
         <v>0</v>
@@ -17994,10 +17994,10 @@
         <v>0</v>
       </c>
       <c r="Y136" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z136" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA136" t="n">
         <v>0</v>
@@ -18048,7 +18048,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Sweden Superettan</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -18058,12 +18058,12 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>GIF Sundsvall</t>
+          <t>Sogndal</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Örgryte</t>
+          <t>Ranheim</t>
         </is>
       </c>
       <c r="G137" t="n">
@@ -18177,22 +18177,22 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Norway First Division</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Lillestrøm</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Stabæk</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="G138" t="n">
@@ -18306,22 +18306,22 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Sweden Superettan</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Mantova</t>
+          <t>Kalmar</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Calcio Padova</t>
+          <t>Falkenberg</t>
         </is>
       </c>
       <c r="G139" t="n">
@@ -18445,12 +18445,12 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Västerås SK</t>
+          <t>Brage</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Varberg</t>
+          <t>Landskrona</t>
         </is>
       </c>
       <c r="G140" t="n">
@@ -18564,22 +18564,22 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Norway First Division</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Akritas</t>
+          <t>Åsane</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Olympiakos</t>
+          <t>Kongsvinger</t>
         </is>
       </c>
       <c r="G141" t="n">
@@ -18688,12 +18688,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group C</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -18703,12 +18703,12 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Lajense</t>
+          <t>Zlín</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Mortágua</t>
+          <t>Bohemians 1905</t>
         </is>
       </c>
       <c r="G142" t="n">
@@ -18808,7 +18808,7 @@
         <v>0</v>
       </c>
       <c r="AK142" s="3" t="n">
-        <v>45969.47916666666</v>
+        <v>45969.45833333334</v>
       </c>
     </row>
     <row r="143">
@@ -18951,7 +18951,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Portugal Campeonato de Portugal Group C</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -18961,12 +18961,12 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Lajense</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Mortágua</t>
         </is>
       </c>
       <c r="G144" t="n">
@@ -18987,13 +18987,13 @@
         </is>
       </c>
       <c r="L144" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="M144" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
@@ -19032,10 +19032,10 @@
         <v>0</v>
       </c>
       <c r="AA144" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AB144" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AC144" t="n">
         <v>0</v>
@@ -19090,12 +19090,12 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayern München</t>
         </is>
       </c>
       <c r="G145" t="n">
@@ -19116,13 +19116,13 @@
         </is>
       </c>
       <c r="L145" t="n">
-        <v>1.38</v>
+        <v>9</v>
       </c>
       <c r="M145" t="n">
-        <v>5</v>
+        <v>6.1</v>
       </c>
       <c r="N145" t="n">
-        <v>7.7</v>
+        <v>1.3</v>
       </c>
       <c r="O145" t="n">
         <v>0</v>
@@ -19161,10 +19161,10 @@
         <v>0</v>
       </c>
       <c r="AA145" t="n">
-        <v>2.2</v>
+        <v>1.93</v>
       </c>
       <c r="AB145" t="n">
-        <v>1.68</v>
+        <v>1.87</v>
       </c>
       <c r="AC145" t="n">
         <v>0</v>
@@ -19219,12 +19219,12 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Hamburger SV</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Borussia Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="G146" t="n">
@@ -19245,13 +19245,13 @@
         </is>
       </c>
       <c r="L146" t="n">
-        <v>4.4</v>
+        <v>2.7</v>
       </c>
       <c r="M146" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="N146" t="n">
-        <v>1.7</v>
+        <v>2.4</v>
       </c>
       <c r="O146" t="n">
         <v>0</v>
@@ -19290,10 +19290,10 @@
         <v>0</v>
       </c>
       <c r="AA146" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AB146" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="AC146" t="n">
         <v>0</v>
@@ -19348,12 +19348,12 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Bayern München</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="G147" t="n">
@@ -19374,13 +19374,13 @@
         </is>
       </c>
       <c r="L147" t="n">
-        <v>9</v>
+        <v>1.38</v>
       </c>
       <c r="M147" t="n">
-        <v>6.1</v>
+        <v>5</v>
       </c>
       <c r="N147" t="n">
-        <v>1.3</v>
+        <v>7.7</v>
       </c>
       <c r="O147" t="n">
         <v>0</v>
@@ -19419,10 +19419,10 @@
         <v>0</v>
       </c>
       <c r="AA147" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AB147" t="n">
-        <v>1.87</v>
+        <v>1.68</v>
       </c>
       <c r="AC147" t="n">
         <v>0</v>
@@ -19467,7 +19467,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -19477,12 +19477,12 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Umm Salal</t>
+          <t>Hamburger SV</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Al Sadd</t>
+          <t>Borussia Dortmund</t>
         </is>
       </c>
       <c r="G148" t="n">
@@ -19503,61 +19503,61 @@
         </is>
       </c>
       <c r="L148" t="n">
-        <v>6.17</v>
+        <v>4.4</v>
       </c>
       <c r="M148" t="n">
-        <v>4.5</v>
+        <v>4.2</v>
       </c>
       <c r="N148" t="n">
-        <v>1.41</v>
+        <v>1.7</v>
       </c>
       <c r="O148" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="P148" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="Q148" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="R148" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S148" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="T148" t="n">
-        <v>1.71</v>
+        <v>0</v>
       </c>
       <c r="U148" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="V148" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W148" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="X148" t="n">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="Y148" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="Z148" t="n">
-        <v>3.61</v>
+        <v>0</v>
       </c>
       <c r="AA148" t="n">
-        <v>1.7</v>
+        <v>2.25</v>
       </c>
       <c r="AB148" t="n">
-        <v>2.05</v>
+        <v>1.65</v>
       </c>
       <c r="AC148" t="n">
-        <v>1.44</v>
+        <v>0</v>
       </c>
       <c r="AD148" t="n">
-        <v>2.66</v>
+        <v>0</v>
       </c>
       <c r="AE148" t="inlineStr">
         <is>
@@ -19570,16 +19570,16 @@
         </is>
       </c>
       <c r="AG148" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AH148" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="AI148" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AJ148" t="n">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="AK148" s="3" t="n">
         <v>45969.47916666666</v>
@@ -19591,12 +19591,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>11:30</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -19606,12 +19606,12 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Umm Salal</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Al Ittifaq</t>
+          <t>Al Sadd</t>
         </is>
       </c>
       <c r="G149" t="n">
@@ -19632,61 +19632,61 @@
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
+        <v>6.17</v>
       </c>
       <c r="M149" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="N149" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="O149" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="P149" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q149" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="R149" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S149" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T149" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U149" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="V149" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W149" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="X149" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="Y149" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z149" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="AA149" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AB149" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AC149" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AD149" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AE149" t="inlineStr">
         <is>
@@ -19699,19 +19699,19 @@
         </is>
       </c>
       <c r="AG149" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AH149" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AI149" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ149" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AK149" s="3" t="n">
-        <v>45969.48958333334</v>
+        <v>45969.47916666666</v>
       </c>
     </row>
     <row r="150">
@@ -19720,12 +19720,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Belgium Pro League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -19735,12 +19735,12 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>Cercle Brugge</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>OH Leuven</t>
+          <t>Al Ittifaq</t>
         </is>
       </c>
       <c r="G150" t="n">
@@ -19761,13 +19761,13 @@
         </is>
       </c>
       <c r="L150" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="M150" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="N150" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="O150" t="n">
         <v>0</v>
@@ -19800,10 +19800,10 @@
         <v>0</v>
       </c>
       <c r="Y150" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z150" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA150" t="n">
         <v>0</v>
@@ -19840,7 +19840,7 @@
         <v>0</v>
       </c>
       <c r="AK150" s="3" t="n">
-        <v>45969.5</v>
+        <v>45969.48958333334</v>
       </c>
     </row>
     <row r="151">
@@ -19854,7 +19854,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -19864,12 +19864,12 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Bristol Rovers</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Glentoran</t>
+          <t>Gillingham</t>
         </is>
       </c>
       <c r="G151" t="n">
@@ -19890,13 +19890,13 @@
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="M151" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="N151" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O151" t="n">
         <v>0</v>
@@ -19929,10 +19929,10 @@
         <v>0</v>
       </c>
       <c r="Y151" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z151" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA151" t="n">
         <v>0</v>
@@ -19983,7 +19983,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -19993,12 +19993,12 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Everton</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Coventry City</t>
         </is>
       </c>
       <c r="G152" t="n">
@@ -20019,13 +20019,13 @@
         </is>
       </c>
       <c r="L152" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="M152" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N152" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="O152" t="n">
         <v>0</v>
@@ -20058,10 +20058,10 @@
         <v>0</v>
       </c>
       <c r="Y152" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="Z152" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="AA152" t="n">
         <v>0</v>
@@ -20112,7 +20112,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -20122,12 +20122,12 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Falkirk</t>
+          <t>Celta de Vigo II</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Livingston</t>
+          <t>Talavera CF</t>
         </is>
       </c>
       <c r="G153" t="n">
@@ -20241,7 +20241,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -20251,12 +20251,12 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Wrexham</t>
+          <t>Exeter City</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Charlton Athletic</t>
+          <t>Wigan Athletic</t>
         </is>
       </c>
       <c r="G154" t="n">
@@ -20277,13 +20277,13 @@
         </is>
       </c>
       <c r="L154" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="M154" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="N154" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="O154" t="n">
         <v>0</v>
@@ -20316,10 +20316,10 @@
         <v>0</v>
       </c>
       <c r="Y154" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Z154" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AA154" t="n">
         <v>0</v>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -20380,12 +20380,12 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Huddersfield Town</t>
+          <t>Swindon Town</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Plymouth Argyle</t>
+          <t>Tranmere Rovers</t>
         </is>
       </c>
       <c r="G155" t="n">
@@ -20412,7 +20412,7 @@
         <v>3.6</v>
       </c>
       <c r="N155" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="O155" t="n">
         <v>0</v>
@@ -20445,16 +20445,16 @@
         <v>0</v>
       </c>
       <c r="Y155" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="Z155" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="AA155" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AB155" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC155" t="n">
         <v>0</v>
@@ -20499,7 +20499,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -20509,12 +20509,12 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>West Ham United</t>
+          <t>Falkirk</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Livingston</t>
         </is>
       </c>
       <c r="G156" t="n">
@@ -20535,13 +20535,13 @@
         </is>
       </c>
       <c r="L156" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M156" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N156" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O156" t="n">
         <v>0</v>
@@ -20574,10 +20574,10 @@
         <v>0</v>
       </c>
       <c r="Y156" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z156" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA156" t="n">
         <v>0</v>
@@ -20628,7 +20628,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -20638,12 +20638,12 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Amora</t>
+          <t>Al Gharafa</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Atlético CP</t>
+          <t>Al Wakrah</t>
         </is>
       </c>
       <c r="G157" t="n">
@@ -20757,7 +20757,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -20767,12 +20767,12 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>CD Trofense</t>
+          <t>Salford City</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>São João Ver</t>
+          <t>Cambridge United</t>
         </is>
       </c>
       <c r="G158" t="n">
@@ -20793,13 +20793,13 @@
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M158" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N158" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="O158" t="n">
         <v>0</v>
@@ -20832,10 +20832,10 @@
         <v>0</v>
       </c>
       <c r="Y158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Z158" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AA158" t="n">
         <v>0</v>
@@ -20886,7 +20886,7 @@
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -20896,12 +20896,12 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Middlesbrough</t>
+          <t>Crawley Town</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Birmingham City</t>
+          <t>Fleetwood Town</t>
         </is>
       </c>
       <c r="G159" t="n">
@@ -20922,13 +20922,13 @@
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M159" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O159" t="n">
         <v>0</v>
@@ -20961,10 +20961,10 @@
         <v>0</v>
       </c>
       <c r="Y159" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z159" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA159" t="n">
         <v>0</v>
@@ -21015,7 +21015,7 @@
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -21025,12 +21025,12 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Barrow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Crusaders</t>
+          <t>Grimsby Town</t>
         </is>
       </c>
       <c r="G160" t="n">
@@ -21051,13 +21051,13 @@
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="M160" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="O160" t="n">
         <v>0</v>
@@ -21090,10 +21090,10 @@
         <v>0</v>
       </c>
       <c r="Y160" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z160" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA160" t="n">
         <v>0</v>
@@ -21144,7 +21144,7 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Campeonato de Portugal Group A</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -21154,12 +21154,12 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Chesterfield</t>
+          <t>Ribeira Brava</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Accrington Stanley</t>
+          <t>Tirsense</t>
         </is>
       </c>
       <c r="G161" t="n">
@@ -21180,13 +21180,13 @@
         </is>
       </c>
       <c r="L161" t="n">
-        <v>1.53</v>
+        <v>0</v>
       </c>
       <c r="M161" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="N161" t="n">
-        <v>5.6</v>
+        <v>0</v>
       </c>
       <c r="O161" t="n">
         <v>0</v>
@@ -21219,10 +21219,10 @@
         <v>0</v>
       </c>
       <c r="Y161" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z161" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AA161" t="n">
         <v>0</v>
@@ -21273,7 +21273,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -21283,12 +21283,12 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Greenock Morton</t>
+          <t>Barnet</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Arbroath</t>
+          <t>Milton Keynes Dons</t>
         </is>
       </c>
       <c r="G162" t="n">
@@ -21309,13 +21309,13 @@
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="M162" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N162" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O162" t="n">
         <v>0</v>
@@ -21348,10 +21348,10 @@
         <v>0</v>
       </c>
       <c r="Y162" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z162" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA162" t="n">
         <v>0</v>
@@ -21402,7 +21402,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Greece Super League</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -21412,12 +21412,12 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Sheffield United</t>
+          <t>Panaitolikos</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Queens Park Rangers</t>
+          <t>Larissa</t>
         </is>
       </c>
       <c r="G163" t="n">
@@ -21438,13 +21438,13 @@
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="M163" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N163" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O163" t="n">
         <v>0</v>
@@ -21477,10 +21477,10 @@
         <v>0</v>
       </c>
       <c r="Y163" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="Z163" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AA163" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Belgium Pro League</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -21541,12 +21541,12 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Rotherham United</t>
+          <t>Cercle Brugge</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Lincoln City</t>
+          <t>OH Leuven</t>
         </is>
       </c>
       <c r="G164" t="n">
@@ -21567,13 +21567,13 @@
         </is>
       </c>
       <c r="L164" t="n">
-        <v>2.95</v>
+        <v>1.97</v>
       </c>
       <c r="M164" t="n">
-        <v>3.15</v>
+        <v>3.75</v>
       </c>
       <c r="N164" t="n">
-        <v>2.35</v>
+        <v>3.6</v>
       </c>
       <c r="O164" t="n">
         <v>0</v>
@@ -21606,10 +21606,10 @@
         <v>0</v>
       </c>
       <c r="Y164" t="n">
-        <v>2.3</v>
+        <v>1.85</v>
       </c>
       <c r="Z164" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AA164" t="n">
         <v>0</v>
@@ -21660,7 +21660,7 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -21670,12 +21670,12 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>Stockport County</t>
+          <t>Bangor</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Luton Town</t>
+          <t>Ballymena United</t>
         </is>
       </c>
       <c r="G165" t="n">
@@ -21696,13 +21696,13 @@
         </is>
       </c>
       <c r="L165" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="M165" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="N165" t="n">
-        <v>3.25</v>
+        <v>0</v>
       </c>
       <c r="O165" t="n">
         <v>0</v>
@@ -21735,10 +21735,10 @@
         <v>0</v>
       </c>
       <c r="Y165" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Z165" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AA165" t="n">
         <v>0</v>
@@ -21789,7 +21789,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -21799,12 +21799,12 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Celta de Vigo II</t>
+          <t>Jeunesse Sportive Omrane</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Talavera CF</t>
+          <t>Olympique Béja</t>
         </is>
       </c>
       <c r="G166" t="n">
@@ -21918,7 +21918,7 @@
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Tunisia Ligue 1</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -21928,12 +21928,12 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>Bradford City</t>
+          <t>Club Africain</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Burton Albion</t>
+          <t>ES Tunis</t>
         </is>
       </c>
       <c r="G167" t="n">
@@ -21954,13 +21954,13 @@
         </is>
       </c>
       <c r="L167" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="M167" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N167" t="n">
-        <v>4.9</v>
+        <v>0</v>
       </c>
       <c r="O167" t="n">
         <v>0</v>
@@ -21993,10 +21993,10 @@
         <v>0</v>
       </c>
       <c r="Y167" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z167" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AA167" t="n">
         <v>0</v>
@@ -22047,7 +22047,7 @@
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -22057,12 +22057,12 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>Doncaster Rovers</t>
+          <t>Newport County</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Barnsley</t>
+          <t>Walsall</t>
         </is>
       </c>
       <c r="G168" t="n">
@@ -22083,13 +22083,13 @@
         </is>
       </c>
       <c r="L168" t="n">
-        <v>2.15</v>
+        <v>4.3</v>
       </c>
       <c r="M168" t="n">
         <v>3.5</v>
       </c>
       <c r="N168" t="n">
-        <v>3.05</v>
+        <v>1.75</v>
       </c>
       <c r="O168" t="n">
         <v>0</v>
@@ -22122,10 +22122,10 @@
         <v>0</v>
       </c>
       <c r="Y168" t="n">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="Z168" t="n">
-        <v>2.02</v>
+        <v>1.72</v>
       </c>
       <c r="AA168" t="n">
         <v>0</v>
@@ -22176,7 +22176,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -22186,12 +22186,12 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Dunfermline Athletic</t>
+          <t>Harrogate Town</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Oldham Athletic</t>
         </is>
       </c>
       <c r="G169" t="n">
@@ -22212,13 +22212,13 @@
         </is>
       </c>
       <c r="L169" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="M169" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="N169" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="O169" t="n">
         <v>0</v>
@@ -22251,10 +22251,10 @@
         <v>0</v>
       </c>
       <c r="Y169" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z169" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA169" t="n">
         <v>0</v>
@@ -22305,7 +22305,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -22315,12 +22315,12 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>Queen's Park</t>
+          <t>Cliftonville</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Raith Rovers</t>
+          <t>Dungannon Swifts</t>
         </is>
       </c>
       <c r="G170" t="n">
@@ -22434,7 +22434,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -22444,12 +22444,12 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Salford City</t>
+          <t>Peterborough United</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Cambridge United</t>
+          <t>AFC Wimbledon</t>
         </is>
       </c>
       <c r="G171" t="n">
@@ -22470,49 +22470,49 @@
         </is>
       </c>
       <c r="L171" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="M171" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N171" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="O171" t="n">
+        <v>0</v>
+      </c>
+      <c r="P171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q171" t="n">
+        <v>0</v>
+      </c>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="n">
+        <v>0</v>
+      </c>
+      <c r="T171" t="n">
+        <v>0</v>
+      </c>
+      <c r="U171" t="n">
+        <v>0</v>
+      </c>
+      <c r="V171" t="n">
+        <v>0</v>
+      </c>
+      <c r="W171" t="n">
+        <v>0</v>
+      </c>
+      <c r="X171" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y171" t="n">
         <v>2.15</v>
       </c>
-      <c r="M171" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="N171" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="O171" t="n">
-        <v>0</v>
-      </c>
-      <c r="P171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
-      <c r="R171" t="n">
-        <v>0</v>
-      </c>
-      <c r="S171" t="n">
-        <v>0</v>
-      </c>
-      <c r="T171" t="n">
-        <v>0</v>
-      </c>
-      <c r="U171" t="n">
-        <v>0</v>
-      </c>
-      <c r="V171" t="n">
-        <v>0</v>
-      </c>
-      <c r="W171" t="n">
-        <v>0</v>
-      </c>
-      <c r="X171" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y171" t="n">
-        <v>2</v>
-      </c>
       <c r="Z171" t="n">
-        <v>1.72</v>
+        <v>1.62</v>
       </c>
       <c r="AA171" t="n">
         <v>0</v>
@@ -22563,7 +22563,7 @@
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>England EFL League Two</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -22573,12 +22573,12 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>Cliftonville</t>
+          <t>Chesterfield</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Dungannon Swifts</t>
+          <t>Accrington Stanley</t>
         </is>
       </c>
       <c r="G172" t="n">
@@ -22599,13 +22599,13 @@
         </is>
       </c>
       <c r="L172" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="M172" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="N172" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="O172" t="n">
         <v>0</v>
@@ -22638,10 +22638,10 @@
         <v>0</v>
       </c>
       <c r="Y172" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z172" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AA172" t="n">
         <v>0</v>
@@ -22692,7 +22692,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -22702,12 +22702,12 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Barrow</t>
+          <t>Bradford City</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Grimsby Town</t>
+          <t>Burton Albion</t>
         </is>
       </c>
       <c r="G173" t="n">
@@ -22728,13 +22728,13 @@
         </is>
       </c>
       <c r="L173" t="n">
-        <v>3.3</v>
+        <v>1.65</v>
       </c>
       <c r="M173" t="n">
-        <v>3.3</v>
+        <v>3.7</v>
       </c>
       <c r="N173" t="n">
-        <v>2.1</v>
+        <v>4.9</v>
       </c>
       <c r="O173" t="n">
         <v>0</v>
@@ -22767,10 +22767,10 @@
         <v>0</v>
       </c>
       <c r="Y173" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="Z173" t="n">
         <v>1.9</v>
-      </c>
-      <c r="Z173" t="n">
-        <v>1.8</v>
       </c>
       <c r="AA173" t="n">
         <v>0</v>
@@ -22821,7 +22821,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Portugal Campeonato de Portugal Group A</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -22831,12 +22831,12 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Ribeira Brava</t>
+          <t>Everton</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>Tirsense</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="G174" t="n">
@@ -22857,13 +22857,13 @@
         </is>
       </c>
       <c r="L174" t="n">
-        <v>0</v>
+        <v>2.13</v>
       </c>
       <c r="M174" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N174" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="O174" t="n">
         <v>0</v>
@@ -22896,10 +22896,10 @@
         <v>0</v>
       </c>
       <c r="Y174" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="Z174" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AA174" t="n">
         <v>0</v>
@@ -22950,7 +22950,7 @@
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Greece Super League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D175" t="inlineStr">
@@ -22960,12 +22960,12 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Panaitolikos</t>
+          <t>Sheffield United</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>Larissa</t>
+          <t>Queens Park Rangers</t>
         </is>
       </c>
       <c r="G175" t="n">
@@ -22986,13 +22986,13 @@
         </is>
       </c>
       <c r="L175" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="M175" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N175" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O175" t="n">
         <v>0</v>
@@ -23025,10 +23025,10 @@
         <v>0</v>
       </c>
       <c r="Y175" t="n">
-        <v>2.13</v>
+        <v>0</v>
       </c>
       <c r="Z175" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AA175" t="n">
         <v>0</v>
@@ -23079,7 +23079,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -23089,12 +23089,12 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Jeunesse Sportive Omrane</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>Olympique Béja</t>
+          <t>Glentoran</t>
         </is>
       </c>
       <c r="G176" t="n">
@@ -23208,7 +23208,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -23218,12 +23218,12 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Bristol Rovers</t>
+          <t>CD Trofense</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>Gillingham</t>
+          <t>São João Ver</t>
         </is>
       </c>
       <c r="G177" t="n">
@@ -23244,13 +23244,13 @@
         </is>
       </c>
       <c r="L177" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="M177" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N177" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O177" t="n">
         <v>0</v>
@@ -23283,10 +23283,10 @@
         <v>0</v>
       </c>
       <c r="Y177" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z177" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA177" t="n">
         <v>0</v>
@@ -23337,7 +23337,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -23347,12 +23347,12 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Exeter City</t>
+          <t>Amora</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>Wigan Athletic</t>
+          <t>Atlético CP</t>
         </is>
       </c>
       <c r="G178" t="n">
@@ -23373,13 +23373,13 @@
         </is>
       </c>
       <c r="L178" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="M178" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="N178" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="O178" t="n">
         <v>0</v>
@@ -23412,10 +23412,10 @@
         <v>0</v>
       </c>
       <c r="Y178" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Z178" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="AA178" t="n">
         <v>0</v>
@@ -23466,7 +23466,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -23476,12 +23476,12 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Norwich City</t>
+          <t>Queen's Park</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>Leicester City</t>
+          <t>Raith Rovers</t>
         </is>
       </c>
       <c r="G179" t="n">
@@ -23595,7 +23595,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -23605,12 +23605,12 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>Swansea City</t>
+          <t>Bolton Wanderers</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Ipswich Town</t>
+          <t>Port Vale</t>
         </is>
       </c>
       <c r="G180" t="n">
@@ -23631,13 +23631,13 @@
         </is>
       </c>
       <c r="L180" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="M180" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N180" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O180" t="n">
         <v>0</v>
@@ -23670,10 +23670,10 @@
         <v>0</v>
       </c>
       <c r="Y180" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z180" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AA180" t="n">
         <v>0</v>
@@ -23724,7 +23724,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -23734,12 +23734,12 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Barnet</t>
+          <t>Blackpool</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>Milton Keynes Dons</t>
+          <t>Cardiff City</t>
         </is>
       </c>
       <c r="G181" t="n">
@@ -23760,13 +23760,13 @@
         </is>
       </c>
       <c r="L181" t="n">
-        <v>1.98</v>
+        <v>3.35</v>
       </c>
       <c r="M181" t="n">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="N181" t="n">
-        <v>3.5</v>
+        <v>2.05</v>
       </c>
       <c r="O181" t="n">
         <v>0</v>
@@ -23799,10 +23799,10 @@
         <v>0</v>
       </c>
       <c r="Y181" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Z181" t="n">
         <v>1.8</v>
-      </c>
-      <c r="Z181" t="n">
-        <v>1.9</v>
       </c>
       <c r="AA181" t="n">
         <v>0</v>
@@ -23853,7 +23853,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -23863,12 +23863,12 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>West Bromwich Albion</t>
+          <t>West Ham United</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>Oxford United</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="G182" t="n">
@@ -23889,13 +23889,13 @@
         </is>
       </c>
       <c r="L182" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M182" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N182" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O182" t="n">
         <v>0</v>
@@ -23928,10 +23928,10 @@
         <v>0</v>
       </c>
       <c r="Y182" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="Z182" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AA182" t="n">
         <v>0</v>
@@ -23982,7 +23982,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Tunisia Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -23992,12 +23992,12 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Club Africain</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>ES Tunis</t>
+          <t>Crusaders</t>
         </is>
       </c>
       <c r="G183" t="n">
@@ -24111,7 +24111,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -24121,12 +24121,12 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>Bangor</t>
+          <t>Dunfermline Athletic</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>Ballymena United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G184" t="n">
@@ -24240,7 +24240,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -24250,12 +24250,12 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Doncaster Rovers</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>Coventry City</t>
+          <t>Barnsley</t>
         </is>
       </c>
       <c r="G185" t="n">
@@ -24276,13 +24276,13 @@
         </is>
       </c>
       <c r="L185" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="M185" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="O185" t="n">
         <v>0</v>
@@ -24315,10 +24315,10 @@
         <v>0</v>
       </c>
       <c r="Y185" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z185" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AA185" t="n">
         <v>0</v>
@@ -24379,12 +24379,12 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Bolton Wanderers</t>
+          <t>Rotherham United</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>Port Vale</t>
+          <t>Lincoln City</t>
         </is>
       </c>
       <c r="G186" t="n">
@@ -24405,13 +24405,13 @@
         </is>
       </c>
       <c r="L186" t="n">
-        <v>1.68</v>
+        <v>2.95</v>
       </c>
       <c r="M186" t="n">
-        <v>3.6</v>
+        <v>3.15</v>
       </c>
       <c r="N186" t="n">
-        <v>4.8</v>
+        <v>2.35</v>
       </c>
       <c r="O186" t="n">
         <v>0</v>
@@ -24444,10 +24444,10 @@
         <v>0</v>
       </c>
       <c r="Y186" t="n">
-        <v>1.97</v>
+        <v>2.3</v>
       </c>
       <c r="Z186" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="AA186" t="n">
         <v>0</v>
@@ -24498,7 +24498,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -24508,12 +24508,12 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>Newport County</t>
+          <t>Ross County</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
         <is>
-          <t>Walsall</t>
+          <t>Ayr United</t>
         </is>
       </c>
       <c r="G187" t="n">
@@ -24534,13 +24534,13 @@
         </is>
       </c>
       <c r="L187" t="n">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="M187" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N187" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="O187" t="n">
         <v>0</v>
@@ -24573,10 +24573,10 @@
         <v>0</v>
       </c>
       <c r="Y187" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Z187" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="AA187" t="n">
         <v>0</v>
@@ -24627,7 +24627,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -24637,12 +24637,12 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>Southampton</t>
+          <t>Greenock Morton</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>Sheffield Wednesday</t>
+          <t>Arbroath</t>
         </is>
       </c>
       <c r="G188" t="n">
@@ -24756,7 +24756,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -24766,12 +24766,12 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Harrogate Town</t>
+          <t>Middlesbrough</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>Oldham Athletic</t>
+          <t>Birmingham City</t>
         </is>
       </c>
       <c r="G189" t="n">
@@ -24792,13 +24792,13 @@
         </is>
       </c>
       <c r="L189" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="M189" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="N189" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="O189" t="n">
         <v>0</v>
@@ -24831,10 +24831,10 @@
         <v>0</v>
       </c>
       <c r="Y189" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z189" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA189" t="n">
         <v>0</v>
@@ -24885,7 +24885,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England EFL League One</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -24895,12 +24895,12 @@
       </c>
       <c r="E190" t="inlineStr">
         <is>
-          <t>Crawley Town</t>
+          <t>Huddersfield Town</t>
         </is>
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>Fleetwood Town</t>
+          <t>Plymouth Argyle</t>
         </is>
       </c>
       <c r="G190" t="n">
@@ -24921,13 +24921,13 @@
         </is>
       </c>
       <c r="L190" t="n">
-        <v>2.13</v>
+        <v>1.85</v>
       </c>
       <c r="M190" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="N190" t="n">
-        <v>3.05</v>
+        <v>3.75</v>
       </c>
       <c r="O190" t="n">
         <v>0</v>
@@ -24960,10 +24960,10 @@
         <v>0</v>
       </c>
       <c r="Y190" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="Z190" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AA190" t="n">
         <v>0</v>
@@ -25014,7 +25014,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -25024,12 +25024,12 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Ross County</t>
+          <t>Norwich City</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>Ayr United</t>
+          <t>Leicester City</t>
         </is>
       </c>
       <c r="G191" t="n">
@@ -25143,7 +25143,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>England EFL League Two</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -25153,12 +25153,12 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Swindon Town</t>
+          <t>Swansea City</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>Tranmere Rovers</t>
+          <t>Ipswich Town</t>
         </is>
       </c>
       <c r="G192" t="n">
@@ -25179,13 +25179,13 @@
         </is>
       </c>
       <c r="L192" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="M192" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N192" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="O192" t="n">
         <v>0</v>
@@ -25218,16 +25218,16 @@
         <v>0</v>
       </c>
       <c r="Y192" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="Z192" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="AA192" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AB192" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC192" t="n">
         <v>0</v>
@@ -25282,12 +25282,12 @@
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Blackpool</t>
+          <t>Stockport County</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>Cardiff City</t>
+          <t>Luton Town</t>
         </is>
       </c>
       <c r="G193" t="n">
@@ -25308,13 +25308,13 @@
         </is>
       </c>
       <c r="L193" t="n">
-        <v>3.35</v>
+        <v>2.15</v>
       </c>
       <c r="M193" t="n">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="N193" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="O193" t="n">
         <v>0</v>
@@ -25347,10 +25347,10 @@
         <v>0</v>
       </c>
       <c r="Y193" t="n">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="Z193" t="n">
-        <v>1.8</v>
+        <v>1.65</v>
       </c>
       <c r="AA193" t="n">
         <v>0</v>
@@ -25401,7 +25401,7 @@
       </c>
       <c r="C194" t="inlineStr">
         <is>
-          <t>England EFL League One</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -25411,12 +25411,12 @@
       </c>
       <c r="E194" t="inlineStr">
         <is>
-          <t>Peterborough United</t>
+          <t>West Bromwich Albion</t>
         </is>
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>AFC Wimbledon</t>
+          <t>Oxford United</t>
         </is>
       </c>
       <c r="G194" t="n">
@@ -25437,13 +25437,13 @@
         </is>
       </c>
       <c r="L194" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="M194" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="N194" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="O194" t="n">
         <v>0</v>
@@ -25476,10 +25476,10 @@
         <v>0</v>
       </c>
       <c r="Y194" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z194" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="AA194" t="n">
         <v>0</v>
@@ -25530,7 +25530,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -25540,12 +25540,12 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Al Gharafa</t>
+          <t>Southampton</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>Al Wakrah</t>
+          <t>Sheffield Wednesday</t>
         </is>
       </c>
       <c r="G195" t="n">
@@ -25654,12 +25654,12 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -25669,12 +25669,12 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Hércules CF</t>
+          <t>Wrexham</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>CE Europa</t>
+          <t>Charlton Athletic</t>
         </is>
       </c>
       <c r="G196" t="n">
@@ -25774,7 +25774,7 @@
         <v>0</v>
       </c>
       <c r="AK196" s="3" t="n">
-        <v>45969.51041666666</v>
+        <v>45969.5</v>
       </c>
     </row>
     <row r="197">
@@ -25788,7 +25788,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -25798,12 +25798,12 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Sevilla FC</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>FC Andorra</t>
+          <t>CA Osasuna</t>
         </is>
       </c>
       <c r="G197" t="n">
@@ -25824,13 +25824,13 @@
         </is>
       </c>
       <c r="L197" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="M197" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>3.71</v>
       </c>
       <c r="O197" t="n">
         <v>0</v>
@@ -25863,10 +25863,10 @@
         <v>0</v>
       </c>
       <c r="Y197" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Z197" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AA197" t="n">
         <v>0</v>
@@ -25917,7 +25917,7 @@
       </c>
       <c r="C198" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -25927,12 +25927,12 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>SD Eibar</t>
+          <t>Arenteiro</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>Albacete Balompié</t>
+          <t>Racing Club de Ferrol</t>
         </is>
       </c>
       <c r="G198" t="n">
@@ -26046,7 +26046,7 @@
       </c>
       <c r="C199" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -26056,12 +26056,12 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Sevilla FC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>CA Osasuna</t>
+          <t>FC Andorra</t>
         </is>
       </c>
       <c r="G199" t="n">
@@ -26082,13 +26082,13 @@
         </is>
       </c>
       <c r="L199" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="M199" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="N199" t="n">
-        <v>3.71</v>
+        <v>0</v>
       </c>
       <c r="O199" t="n">
         <v>0</v>
@@ -26121,10 +26121,10 @@
         <v>0</v>
       </c>
       <c r="Y199" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Z199" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AA199" t="n">
         <v>0</v>
@@ -26175,7 +26175,7 @@
       </c>
       <c r="C200" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -26185,12 +26185,12 @@
       </c>
       <c r="E200" t="inlineStr">
         <is>
-          <t>Arenteiro</t>
+          <t>SD Eibar</t>
         </is>
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>Racing Club de Ferrol</t>
+          <t>Albacete Balompié</t>
         </is>
       </c>
       <c r="G200" t="n">
@@ -26299,12 +26299,12 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>12:30</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 1</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -26314,12 +26314,12 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Atlético Astorga FC</t>
+          <t>Hércules CF</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>UD Ourense</t>
+          <t>CE Europa</t>
         </is>
       </c>
       <c r="G201" t="n">
@@ -26419,7 +26419,7 @@
         <v>0</v>
       </c>
       <c r="AK201" s="3" t="n">
-        <v>45969.52083333334</v>
+        <v>45969.51041666666</v>
       </c>
     </row>
     <row r="202">
@@ -26433,7 +26433,7 @@
       </c>
       <c r="C202" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Spain Segunda División RFEF Group 1</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -26443,12 +26443,12 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Athletic Club W</t>
+          <t>Atlético Astorga FC</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>Eibar W</t>
+          <t>UD Ourense</t>
         </is>
       </c>
       <c r="G202" t="n">
@@ -26562,7 +26562,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -26572,12 +26572,12 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="G203" t="n">
@@ -26598,13 +26598,13 @@
         </is>
       </c>
       <c r="L203" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="M203" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="N203" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O203" t="n">
         <v>0</v>
@@ -26643,10 +26643,10 @@
         <v>0</v>
       </c>
       <c r="AA203" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AB203" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC203" t="n">
         <v>0</v>
@@ -26820,7 +26820,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -26830,12 +26830,12 @@
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>Dinamo Bucureşti</t>
+          <t>Saarbrucken</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>Csikszereda</t>
+          <t>Havelse</t>
         </is>
       </c>
       <c r="G205" t="n">
@@ -26856,13 +26856,13 @@
         </is>
       </c>
       <c r="L205" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="M205" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="N205" t="n">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="O205" t="n">
         <v>0</v>
@@ -26895,10 +26895,10 @@
         <v>0</v>
       </c>
       <c r="Y205" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="Z205" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="AA205" t="n">
         <v>0</v>
@@ -26949,22 +26949,22 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>La Serena</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="G206" t="n">
@@ -26985,13 +26985,13 @@
         </is>
       </c>
       <c r="L206" t="n">
-        <v>3.26</v>
+        <v>2.02</v>
       </c>
       <c r="M206" t="n">
-        <v>3.28</v>
+        <v>3.9</v>
       </c>
       <c r="N206" t="n">
-        <v>2.16</v>
+        <v>3.35</v>
       </c>
       <c r="O206" t="n">
         <v>0</v>
@@ -27030,10 +27030,10 @@
         <v>0</v>
       </c>
       <c r="AA206" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AB206" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AC206" t="n">
         <v>0</v>
@@ -27078,7 +27078,7 @@
       </c>
       <c r="C207" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -27088,12 +27088,12 @@
       </c>
       <c r="E207" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dinamo Bucureşti</t>
         </is>
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="G207" t="n">
@@ -27114,13 +27114,13 @@
         </is>
       </c>
       <c r="L207" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="M207" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="N207" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="O207" t="n">
         <v>0</v>
@@ -27153,10 +27153,10 @@
         <v>0</v>
       </c>
       <c r="Y207" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Z207" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AA207" t="n">
         <v>0</v>
@@ -27207,7 +27207,7 @@
       </c>
       <c r="C208" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -27217,12 +27217,12 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Saarbrucken</t>
+          <t>Athletic Club W</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>Havelse</t>
+          <t>Eibar W</t>
         </is>
       </c>
       <c r="G208" t="n">
@@ -27331,27 +27331,27 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:30</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
         <is>
-          <t>Spain Segunda División RFEF Group 5</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>Colonia Moscardó</t>
+          <t>La Serena</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>Elche II</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="G209" t="n">
@@ -27372,13 +27372,13 @@
         </is>
       </c>
       <c r="L209" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="M209" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="N209" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O209" t="n">
         <v>0</v>
@@ -27451,7 +27451,7 @@
         <v>0</v>
       </c>
       <c r="AK209" s="3" t="n">
-        <v>45969.54166666666</v>
+        <v>45969.52083333334</v>
       </c>
     </row>
     <row r="210">
@@ -27465,7 +27465,7 @@
       </c>
       <c r="C210" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D210" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Líšeň</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="G210" t="n">
@@ -27594,7 +27594,7 @@
       </c>
       <c r="C211" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D211" t="inlineStr">
@@ -27604,12 +27604,12 @@
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Radomlje</t>
+          <t>Líšeň</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G211" t="n">
@@ -27723,7 +27723,7 @@
       </c>
       <c r="C212" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -27733,12 +27733,12 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Ethnikos Achna</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>Apollon</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="G212" t="n">
@@ -27852,7 +27852,7 @@
       </c>
       <c r="C213" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -27862,12 +27862,12 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Olympique Marseille</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G213" t="n">
@@ -27888,13 +27888,13 @@
         </is>
       </c>
       <c r="L213" t="n">
-        <v>1.38</v>
+        <v>0</v>
       </c>
       <c r="M213" t="n">
-        <v>5.1</v>
+        <v>0</v>
       </c>
       <c r="N213" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="O213" t="n">
         <v>0</v>
@@ -27927,10 +27927,10 @@
         <v>0</v>
       </c>
       <c r="Y213" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z213" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA213" t="n">
         <v>0</v>
@@ -27981,7 +27981,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -27991,12 +27991,12 @@
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Lokomotiv Plovdiv</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Beroe</t>
         </is>
       </c>
       <c r="G214" t="n">
@@ -28017,13 +28017,13 @@
         </is>
       </c>
       <c r="L214" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="M214" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="N214" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O214" t="n">
         <v>0</v>
@@ -28056,10 +28056,10 @@
         <v>0</v>
       </c>
       <c r="Y214" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="Z214" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AA214" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -28120,12 +28120,12 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Ethnikos Achna</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Apollon</t>
         </is>
       </c>
       <c r="G215" t="n">
@@ -28239,7 +28239,7 @@
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -28249,12 +28249,12 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Celje</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Bravo</t>
         </is>
       </c>
       <c r="G216" t="n">
@@ -28368,7 +28368,7 @@
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Turkey 1. Lig</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Amed</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Hatayspor</t>
         </is>
       </c>
       <c r="G217" t="n">
@@ -28497,7 +28497,7 @@
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>Ried</t>
+          <t>Mura</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
         <is>
-          <t>Blau-Weiß Linz</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G218" t="n">
@@ -28533,13 +28533,13 @@
         </is>
       </c>
       <c r="L218" t="n">
-        <v>2.27</v>
+        <v>0</v>
       </c>
       <c r="M218" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="N218" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O218" t="n">
         <v>0</v>
@@ -28572,10 +28572,10 @@
         <v>0</v>
       </c>
       <c r="Y218" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z218" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AA218" t="n">
         <v>0</v>
@@ -28626,7 +28626,7 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Spain Segunda División RFEF Group 5</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
@@ -28636,12 +28636,12 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Colonia Moscardó</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Elche II</t>
         </is>
       </c>
       <c r="G219" t="n">
@@ -28755,7 +28755,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -28765,12 +28765,12 @@
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>Wolfsberger AC</t>
+          <t>Olimpija</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>Hartberg</t>
+          <t>NK Primorje</t>
         </is>
       </c>
       <c r="G220" t="n">
@@ -28791,13 +28791,13 @@
         </is>
       </c>
       <c r="L220" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="M220" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N220" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="O220" t="n">
         <v>0</v>
@@ -28830,10 +28830,10 @@
         <v>0</v>
       </c>
       <c r="Y220" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z220" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="AA220" t="n">
         <v>0</v>
@@ -28884,7 +28884,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -28894,12 +28894,12 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Lokomotiv Plovdiv</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
         <is>
-          <t>Beroe</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G221" t="n">
@@ -28920,13 +28920,13 @@
         </is>
       </c>
       <c r="L221" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="M221" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="N221" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O221" t="n">
         <v>0</v>
@@ -28959,10 +28959,10 @@
         <v>0</v>
       </c>
       <c r="Y221" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="Z221" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AA221" t="n">
         <v>0</v>
@@ -29013,7 +29013,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -29023,12 +29023,12 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="G222" t="n">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="G223" t="n">
@@ -29281,12 +29281,12 @@
       </c>
       <c r="E224" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G224" t="n">
@@ -29400,7 +29400,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -29410,12 +29410,12 @@
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Olimpija</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
         <is>
-          <t>NK Primorje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G225" t="n">
@@ -29529,7 +29529,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -29539,12 +29539,12 @@
       </c>
       <c r="E226" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G226" t="n">
@@ -29658,7 +29658,7 @@
       </c>
       <c r="C227" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D227" t="inlineStr">
@@ -29668,12 +29668,12 @@
       </c>
       <c r="E227" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Dire Dawa Kenema</t>
         </is>
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Welwalo Adigrat Uni</t>
         </is>
       </c>
       <c r="G227" t="n">
@@ -29787,7 +29787,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -29797,12 +29797,12 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Mura</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="G228" t="n">
@@ -29916,7 +29916,7 @@
       </c>
       <c r="C229" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D229" t="inlineStr">
@@ -29926,12 +29926,12 @@
       </c>
       <c r="E229" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G229" t="n">
@@ -30045,7 +30045,7 @@
       </c>
       <c r="C230" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D230" t="inlineStr">
@@ -30055,12 +30055,12 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Olympique Marseille</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="G230" t="n">
@@ -30081,13 +30081,13 @@
         </is>
       </c>
       <c r="L230" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M230" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="O230" t="n">
         <v>0</v>
@@ -30120,10 +30120,10 @@
         <v>0</v>
       </c>
       <c r="Y230" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z230" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA230" t="n">
         <v>0</v>
@@ -30174,7 +30174,7 @@
       </c>
       <c r="C231" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D231" t="inlineStr">
@@ -30184,12 +30184,12 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Celje</t>
+          <t>Wolfsberger AC</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>Bravo</t>
+          <t>Hartberg</t>
         </is>
       </c>
       <c r="G231" t="n">
@@ -30210,13 +30210,13 @@
         </is>
       </c>
       <c r="L231" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="M231" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="O231" t="n">
         <v>0</v>
@@ -30249,10 +30249,10 @@
         <v>0</v>
       </c>
       <c r="Y231" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z231" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="AA231" t="n">
         <v>0</v>
@@ -30303,7 +30303,7 @@
       </c>
       <c r="C232" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D232" t="inlineStr">
@@ -30313,12 +30313,12 @@
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Ried</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Blau-Weiß Linz</t>
         </is>
       </c>
       <c r="G232" t="n">
@@ -30339,13 +30339,13 @@
         </is>
       </c>
       <c r="L232" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="M232" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="N232" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O232" t="n">
         <v>0</v>
@@ -30378,10 +30378,10 @@
         <v>0</v>
       </c>
       <c r="Y232" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z232" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AA232" t="n">
         <v>0</v>
@@ -30432,7 +30432,7 @@
       </c>
       <c r="C233" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D233" t="inlineStr">
@@ -30442,12 +30442,12 @@
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>Austria Wien</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
         <is>
-          <t>Grazer AK</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G233" t="n">
@@ -30468,13 +30468,13 @@
         </is>
       </c>
       <c r="L233" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="M233" t="n">
-        <v>3.95</v>
+        <v>0</v>
       </c>
       <c r="N233" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="O233" t="n">
         <v>0</v>
@@ -30507,10 +30507,10 @@
         <v>0</v>
       </c>
       <c r="Y233" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="Z233" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AA233" t="n">
         <v>0</v>
@@ -30561,7 +30561,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>Ethiopia Ethiopia Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -30571,12 +30571,12 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Dire Dawa Kenema</t>
+          <t>Austria Wien</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
         <is>
-          <t>Welwalo Adigrat Uni</t>
+          <t>Grazer AK</t>
         </is>
       </c>
       <c r="G234" t="n">
@@ -30597,13 +30597,13 @@
         </is>
       </c>
       <c r="L234" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="M234" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="N234" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="O234" t="n">
         <v>0</v>
@@ -30636,10 +30636,10 @@
         <v>0</v>
       </c>
       <c r="Y234" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z234" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AA234" t="n">
         <v>0</v>
@@ -30685,12 +30685,12 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
         <is>
-          <t>Turkey 1. Lig</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D235" t="inlineStr">
@@ -30700,12 +30700,12 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Amed</t>
+          <t>Juve Stabia</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>Hatayspor</t>
+          <t>Palermo</t>
         </is>
       </c>
       <c r="G235" t="n">
@@ -30805,7 +30805,7 @@
         <v>0</v>
       </c>
       <c r="AK235" s="3" t="n">
-        <v>45969.54166666666</v>
+        <v>45969.55208333334</v>
       </c>
     </row>
     <row r="236">
@@ -30814,12 +30814,12 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -30829,12 +30829,12 @@
       </c>
       <c r="E236" t="inlineStr">
         <is>
-          <t>Juve Stabia</t>
+          <t>Pianese</t>
         </is>
       </c>
       <c r="F236" t="inlineStr">
         <is>
-          <t>Palermo</t>
+          <t>Rimini</t>
         </is>
       </c>
       <c r="G236" t="n">
@@ -30934,7 +30934,7 @@
         <v>0</v>
       </c>
       <c r="AK236" s="3" t="n">
-        <v>45969.55208333334</v>
+        <v>45969.5625</v>
       </c>
     </row>
     <row r="237">
@@ -30948,7 +30948,7 @@
       </c>
       <c r="C237" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group C</t>
         </is>
       </c>
       <c r="D237" t="inlineStr">
@@ -30958,12 +30958,12 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Cosenza</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
         <is>
-          <t>Wisła Płock</t>
+          <t>Virtus Casarano</t>
         </is>
       </c>
       <c r="G237" t="n">
@@ -31077,7 +31077,7 @@
       </c>
       <c r="C238" t="inlineStr">
         <is>
-          <t>Italy Serie C Group C</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D238" t="inlineStr">
@@ -31087,12 +31087,12 @@
       </c>
       <c r="E238" t="inlineStr">
         <is>
-          <t>Cosenza</t>
+          <t>Ravenna</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
         <is>
-          <t>Virtus Casarano</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G238" t="n">
@@ -31206,7 +31206,7 @@
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Qatar Stars League</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
@@ -31216,12 +31216,12 @@
       </c>
       <c r="E239" t="inlineStr">
         <is>
-          <t>Pro Patria</t>
+          <t>Al Duhail</t>
         </is>
       </c>
       <c r="F239" t="inlineStr">
         <is>
-          <t>Lumezzane</t>
+          <t>Al Sailiya</t>
         </is>
       </c>
       <c r="G239" t="n">
@@ -31335,7 +31335,7 @@
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D240" t="inlineStr">
@@ -31345,12 +31345,12 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>Ravenna</t>
+          <t>Radomlje</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G240" t="n">
@@ -31464,7 +31464,7 @@
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -31474,12 +31474,12 @@
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>Nuova Monterosi</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
         <is>
-          <t>Pontedera</t>
+          <t>Wisła Płock</t>
         </is>
       </c>
       <c r="G241" t="n">
@@ -31593,7 +31593,7 @@
       </c>
       <c r="C242" t="inlineStr">
         <is>
-          <t>Qatar Stars League</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D242" t="inlineStr">
@@ -31603,12 +31603,12 @@
       </c>
       <c r="E242" t="inlineStr">
         <is>
-          <t>Al Duhail</t>
+          <t>Nuova Monterosi</t>
         </is>
       </c>
       <c r="F242" t="inlineStr">
         <is>
-          <t>Al Sailiya</t>
+          <t>Pontedera</t>
         </is>
       </c>
       <c r="G242" t="n">
@@ -31722,7 +31722,7 @@
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D243" t="inlineStr">
@@ -31732,12 +31732,12 @@
       </c>
       <c r="E243" t="inlineStr">
         <is>
-          <t>Pianese</t>
+          <t>Pro Patria</t>
         </is>
       </c>
       <c r="F243" t="inlineStr">
         <is>
-          <t>Rimini</t>
+          <t>Lumezzane</t>
         </is>
       </c>
       <c r="G243" t="n">
@@ -31980,22 +31980,22 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>Los Angeles FC</t>
+          <t>Algeciras CF</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
         <is>
-          <t>Austin</t>
+          <t>Antequera CF</t>
         </is>
       </c>
       <c r="G245" t="n">
@@ -32109,7 +32109,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -32119,12 +32119,12 @@
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Zürich</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
         <is>
-          <t>Aarau</t>
+          <t>Luzern</t>
         </is>
       </c>
       <c r="G246" t="n">
@@ -32238,7 +32238,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>Czech Republic First League</t>
+          <t>Switzerland Super League</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -32248,12 +32248,12 @@
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Baník Ostrava</t>
+          <t>Winterthur</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
         <is>
-          <t>Jablonec</t>
+          <t>Grasshopper</t>
         </is>
       </c>
       <c r="G247" t="n">
@@ -32367,7 +32367,7 @@
       </c>
       <c r="C248" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D248" t="inlineStr">
@@ -32377,12 +32377,12 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Associação Académica de Coimbra OAF</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
         <is>
-          <t>1 Dezembro</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="G248" t="n">
@@ -32496,7 +32496,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Turkey Süper Lig</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -32506,12 +32506,12 @@
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>Algeciras CF</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
         <is>
-          <t>Antequera CF</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="G249" t="n">
@@ -32625,7 +32625,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Croatia Druga HNL</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -32635,12 +32635,12 @@
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>Juventus</t>
+          <t>Sesvete</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
         <is>
-          <t>Torino</t>
+          <t>Opatija</t>
         </is>
       </c>
       <c r="G250" t="n">
@@ -32661,13 +32661,13 @@
         </is>
       </c>
       <c r="L250" t="n">
-        <v>1.48</v>
+        <v>0</v>
       </c>
       <c r="M250" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="N250" t="n">
-        <v>7.3</v>
+        <v>0</v>
       </c>
       <c r="O250" t="n">
         <v>0</v>
@@ -32700,10 +32700,10 @@
         <v>0</v>
       </c>
       <c r="Y250" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Z250" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AA250" t="n">
         <v>0</v>
@@ -32754,22 +32754,22 @@
       </c>
       <c r="C251" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D251" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>Minnesota United</t>
+          <t>Associação Académica de Coimbra OAF</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
         <is>
-          <t>Seattle Sounders</t>
+          <t>1 Dezembro</t>
         </is>
       </c>
       <c r="G251" t="n">
@@ -32883,7 +32883,7 @@
       </c>
       <c r="C252" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D252" t="inlineStr">
@@ -32893,12 +32893,12 @@
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Unionistas de Salamanca CF</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Pontevedra CF</t>
         </is>
       </c>
       <c r="G252" t="n">
@@ -33012,22 +33012,22 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Turkey Süper Lig</t>
+          <t>Norway Eliteserien</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Viking</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>HamKam</t>
         </is>
       </c>
       <c r="G253" t="n">
@@ -33141,22 +33141,22 @@
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Cyprus First Division</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>FC Cincinnati</t>
+          <t>Aris</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
         <is>
-          <t>Columbus Crew</t>
+          <t>Digenis Ypsonas</t>
         </is>
       </c>
       <c r="G254" t="n">
@@ -33270,7 +33270,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>Croatia Druga HNL</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -33280,12 +33280,12 @@
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Sesvete</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
         <is>
-          <t>Opatija</t>
+          <t>Aarau</t>
         </is>
       </c>
       <c r="G255" t="n">
@@ -33399,7 +33399,7 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Norway Eliteserien</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
@@ -33409,12 +33409,12 @@
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>Viking</t>
+          <t>Inter Miami</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
         <is>
-          <t>HamKam</t>
+          <t>Nashville SC</t>
         </is>
       </c>
       <c r="G256" t="n">
@@ -33538,12 +33538,12 @@
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>Philadelphia Union</t>
+          <t>Los Angeles FC</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
         <is>
-          <t>Chicago Fire</t>
+          <t>Austin</t>
         </is>
       </c>
       <c r="G257" t="n">
@@ -33657,7 +33657,7 @@
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D258" t="inlineStr">
@@ -33667,12 +33667,12 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Unionistas de Salamanca CF</t>
+          <t>Juventus</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>Pontevedra CF</t>
+          <t>Torino</t>
         </is>
       </c>
       <c r="G258" t="n">
@@ -33693,13 +33693,13 @@
         </is>
       </c>
       <c r="L258" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="M258" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="N258" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O258" t="n">
         <v>0</v>
@@ -33732,10 +33732,10 @@
         <v>0</v>
       </c>
       <c r="Y258" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Z258" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AA258" t="n">
         <v>0</v>
@@ -33786,22 +33786,22 @@
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Cyprus First Division</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aris</t>
+          <t>Minnesota United</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
         <is>
-          <t>Digenis Ypsonas</t>
+          <t>Seattle Sounders</t>
         </is>
       </c>
       <c r="G259" t="n">
@@ -33915,22 +33915,22 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E260" t="inlineStr">
         <is>
-          <t>Zürich</t>
+          <t>Philadelphia Union</t>
         </is>
       </c>
       <c r="F260" t="inlineStr">
         <is>
-          <t>Luzern</t>
+          <t>Chicago Fire</t>
         </is>
       </c>
       <c r="G260" t="n">
@@ -34044,22 +34044,22 @@
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Switzerland Super League</t>
+          <t>USA MLS</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E261" t="inlineStr">
         <is>
-          <t>Winterthur</t>
+          <t>FC Cincinnati</t>
         </is>
       </c>
       <c r="F261" t="inlineStr">
         <is>
-          <t>Grasshopper</t>
+          <t>Columbus Crew</t>
         </is>
       </c>
       <c r="G261" t="n">
@@ -34173,22 +34173,22 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>USA MLS</t>
+          <t>Czech Republic First League</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
         <is>
-          <t>Inter Miami</t>
+          <t>Baník Ostrava</t>
         </is>
       </c>
       <c r="F262" t="inlineStr">
         <is>
-          <t>Nashville SC</t>
+          <t>Jablonec</t>
         </is>
       </c>
       <c r="G262" t="n">
@@ -34431,7 +34431,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -34441,12 +34441,12 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Borussia M'gladbach</t>
+          <t>Deportivo La Coruña</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
         <is>
-          <t>Köln</t>
+          <t>Cultural y Deportiva Leonesa</t>
         </is>
       </c>
       <c r="G264" t="n">
@@ -34467,13 +34467,13 @@
         </is>
       </c>
       <c r="L264" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="M264" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="N264" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="O264" t="n">
         <v>0</v>
@@ -34506,16 +34506,16 @@
         <v>0</v>
       </c>
       <c r="Y264" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="Z264" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="AA264" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="AB264" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="AC264" t="n">
         <v>0</v>
@@ -34560,7 +34560,7 @@
       </c>
       <c r="C265" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D265" t="inlineStr">
@@ -34570,12 +34570,12 @@
       </c>
       <c r="E265" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F265" t="inlineStr">
         <is>
-          <t>Al Ahli</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="G265" t="n">
@@ -34596,13 +34596,13 @@
         </is>
       </c>
       <c r="L265" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="M265" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="N265" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="O265" t="n">
         <v>0</v>
@@ -34635,10 +34635,10 @@
         <v>0</v>
       </c>
       <c r="Y265" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="Z265" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AA265" t="n">
         <v>0</v>
@@ -34818,7 +34818,7 @@
       </c>
       <c r="C267" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D267" t="inlineStr">
@@ -34828,12 +34828,12 @@
       </c>
       <c r="E267" t="inlineStr">
         <is>
-          <t>CD Tenerife</t>
+          <t>Atlético Madrid</t>
         </is>
       </c>
       <c r="F267" t="inlineStr">
         <is>
-          <t>Athletic Club II</t>
+          <t>Levante UD</t>
         </is>
       </c>
       <c r="G267" t="n">
@@ -34854,13 +34854,13 @@
         </is>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="M267" t="n">
-        <v>0</v>
+        <v>6.85</v>
       </c>
       <c r="N267" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O267" t="n">
         <v>0</v>
@@ -34893,10 +34893,10 @@
         <v>0</v>
       </c>
       <c r="Y267" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z267" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="AA267" t="n">
         <v>0</v>
@@ -34947,7 +34947,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -34957,12 +34957,12 @@
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>Atlético Madrid</t>
+          <t>CD Tenerife</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
         <is>
-          <t>Levante UD</t>
+          <t>Athletic Club II</t>
         </is>
       </c>
       <c r="G268" t="n">
@@ -34983,13 +34983,13 @@
         </is>
       </c>
       <c r="L268" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="M268" t="n">
-        <v>6.85</v>
+        <v>0</v>
       </c>
       <c r="N268" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="O268" t="n">
         <v>0</v>
@@ -35022,10 +35022,10 @@
         <v>0</v>
       </c>
       <c r="Y268" t="n">
-        <v>1.5</v>
+        <v>0</v>
       </c>
       <c r="Z268" t="n">
-        <v>2.62</v>
+        <v>0</v>
       </c>
       <c r="AA268" t="n">
         <v>0</v>
@@ -35076,7 +35076,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -35086,12 +35086,12 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Deportivo La Coruña</t>
+          <t>Borussia M'gladbach</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
         <is>
-          <t>Cultural y Deportiva Leonesa</t>
+          <t>Köln</t>
         </is>
       </c>
       <c r="G269" t="n">
@@ -35112,13 +35112,13 @@
         </is>
       </c>
       <c r="L269" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="M269" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="N269" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="O269" t="n">
         <v>0</v>
@@ -35151,16 +35151,16 @@
         <v>0</v>
       </c>
       <c r="Y269" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z269" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AA269" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AB269" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AC269" t="n">
         <v>0</v>
@@ -35205,7 +35205,7 @@
       </c>
       <c r="C270" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Saudi Arabia Professional League</t>
         </is>
       </c>
       <c r="D270" t="inlineStr">
@@ -35215,12 +35215,12 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Al Ittihad</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Al Ahli</t>
         </is>
       </c>
       <c r="G270" t="n">
@@ -35241,13 +35241,13 @@
         </is>
       </c>
       <c r="L270" t="n">
-        <v>7.1</v>
+        <v>0</v>
       </c>
       <c r="M270" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="N270" t="n">
-        <v>1.43</v>
+        <v>0</v>
       </c>
       <c r="O270" t="n">
         <v>0</v>
@@ -35280,10 +35280,10 @@
         <v>0</v>
       </c>
       <c r="Y270" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Z270" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AA270" t="n">
         <v>0</v>
@@ -35334,7 +35334,7 @@
       </c>
       <c r="C271" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Scotland Premiership</t>
         </is>
       </c>
       <c r="D271" t="inlineStr">
@@ -35344,12 +35344,12 @@
       </c>
       <c r="E271" t="inlineStr">
         <is>
-          <t>Volendam</t>
+          <t>St. Mirren</t>
         </is>
       </c>
       <c r="F271" t="inlineStr">
         <is>
-          <t>NAC Breda</t>
+          <t>Hibernian</t>
         </is>
       </c>
       <c r="G271" t="n">
@@ -35370,13 +35370,13 @@
         </is>
       </c>
       <c r="L271" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="M271" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="N271" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="O271" t="n">
         <v>0</v>
@@ -35409,10 +35409,10 @@
         <v>0</v>
       </c>
       <c r="Y271" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Z271" t="n">
-        <v>2.35</v>
+        <v>0</v>
       </c>
       <c r="AA271" t="n">
         <v>0</v>
@@ -35463,7 +35463,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>Scotland Premiership</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -35473,12 +35473,12 @@
       </c>
       <c r="E272" t="inlineStr">
         <is>
-          <t>St. Mirren</t>
+          <t>Volendam</t>
         </is>
       </c>
       <c r="F272" t="inlineStr">
         <is>
-          <t>Hibernian</t>
+          <t>NAC Breda</t>
         </is>
       </c>
       <c r="G272" t="n">
@@ -35499,13 +35499,13 @@
         </is>
       </c>
       <c r="L272" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="M272" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="N272" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="O272" t="n">
         <v>0</v>
@@ -35538,10 +35538,10 @@
         <v>0</v>
       </c>
       <c r="Y272" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z272" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AA272" t="n">
         <v>0</v>
@@ -35721,7 +35721,7 @@
       </c>
       <c r="C274" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D274" t="inlineStr">
@@ -35731,12 +35731,12 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>CD Tondela</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
         <is>
-          <t>Vitória Guimarães</t>
+          <t>Porto II</t>
         </is>
       </c>
       <c r="G274" t="n">
@@ -35850,22 +35850,22 @@
       </c>
       <c r="C275" t="inlineStr">
         <is>
-          <t>Spain Primera Division Women</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D275" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E275" t="inlineStr">
         <is>
-          <t>Real Madrid W</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F275" t="inlineStr">
         <is>
-          <t>Alhama</t>
+          <t>Colo-Colo</t>
         </is>
       </c>
       <c r="G275" t="n">
@@ -36108,7 +36108,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -36118,12 +36118,12 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Botafogo SP</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
         <is>
-          <t>Colo-Colo</t>
+          <t>Amazonas</t>
         </is>
       </c>
       <c r="G277" t="n">
@@ -36237,22 +36237,22 @@
       </c>
       <c r="C278" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
         <is>
-          <t>Botafogo SP</t>
+          <t>Benfica II</t>
         </is>
       </c>
       <c r="F278" t="inlineStr">
         <is>
-          <t>Amazonas</t>
+          <t>FC Vizela</t>
         </is>
       </c>
       <c r="G278" t="n">
@@ -36366,7 +36366,7 @@
       </c>
       <c r="C279" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D279" t="inlineStr">
@@ -36376,12 +36376,12 @@
       </c>
       <c r="E279" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>CD Tondela</t>
         </is>
       </c>
       <c r="F279" t="inlineStr">
         <is>
-          <t>Porto II</t>
+          <t>Vitória Guimarães</t>
         </is>
       </c>
       <c r="G279" t="n">
@@ -36495,7 +36495,7 @@
       </c>
       <c r="C280" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Spain Primera Division Women</t>
         </is>
       </c>
       <c r="D280" t="inlineStr">
@@ -36505,12 +36505,12 @@
       </c>
       <c r="E280" t="inlineStr">
         <is>
-          <t>Benfica II</t>
+          <t>Real Madrid W</t>
         </is>
       </c>
       <c r="F280" t="inlineStr">
         <is>
-          <t>FC Vizela</t>
+          <t>Alhama</t>
         </is>
       </c>
       <c r="G280" t="n">
@@ -36753,7 +36753,7 @@
       </c>
       <c r="C282" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie B</t>
         </is>
       </c>
       <c r="D282" t="inlineStr">
@@ -36763,12 +36763,12 @@
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Stal Mielec</t>
+          <t>Venezia</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
         <is>
-          <t>Pogoń Siedlce</t>
+          <t>Sampdoria</t>
         </is>
       </c>
       <c r="G282" t="n">
@@ -36892,12 +36892,12 @@
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Wieczysta Kraków</t>
+          <t>Stal Mielec</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Pogoń Siedlce</t>
         </is>
       </c>
       <c r="G283" t="n">
@@ -37021,12 +37021,12 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>ŁKS Łódź</t>
+          <t>Wieczysta Kraków</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
         <is>
-          <t>Puszcza Niepołomice</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G284" t="n">
@@ -37140,7 +37140,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Italy Serie B</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -37150,12 +37150,12 @@
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>Venezia</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
         <is>
-          <t>Sampdoria</t>
+          <t>Argeș</t>
         </is>
       </c>
       <c r="G285" t="n">
@@ -37176,13 +37176,13 @@
         </is>
       </c>
       <c r="L285" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="M285" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="N285" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O285" t="n">
         <v>0</v>
@@ -37215,10 +37215,10 @@
         <v>0</v>
       </c>
       <c r="Y285" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="Z285" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AA285" t="n">
         <v>0</v>
@@ -37269,7 +37269,7 @@
       </c>
       <c r="C286" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D286" t="inlineStr">
@@ -37279,12 +37279,12 @@
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>ŁKS Łódź</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
         <is>
-          <t>Argeș</t>
+          <t>Puszcza Niepołomice</t>
         </is>
       </c>
       <c r="G286" t="n">
@@ -37305,13 +37305,13 @@
         </is>
       </c>
       <c r="L286" t="n">
-        <v>1.55</v>
+        <v>0</v>
       </c>
       <c r="M286" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="N286" t="n">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="O286" t="n">
         <v>0</v>
@@ -37344,10 +37344,10 @@
         <v>0</v>
       </c>
       <c r="Y286" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="Z286" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AA286" t="n">
         <v>0</v>
@@ -37398,7 +37398,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -37408,12 +37408,12 @@
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>KV Kortrijk</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="G287" t="n">
@@ -37527,22 +37527,22 @@
       </c>
       <c r="C288" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D288" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>Sport Recife</t>
+          <t>Fortuna Sittard</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
         <is>
-          <t>Atlético Mineiro</t>
+          <t>Heerenveen</t>
         </is>
       </c>
       <c r="G288" t="n">
@@ -37563,13 +37563,13 @@
         </is>
       </c>
       <c r="L288" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="M288" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="N288" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="O288" t="n">
         <v>0</v>
@@ -37602,10 +37602,10 @@
         <v>0</v>
       </c>
       <c r="Y288" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z288" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA288" t="n">
         <v>0</v>
@@ -37666,12 +37666,12 @@
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="G289" t="n">
@@ -37785,7 +37785,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>Portugal Liga 3</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -37795,12 +37795,12 @@
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>Paredes</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
         <is>
-          <t>Sporting Braga II</t>
+          <t>Lokeren-Temse</t>
         </is>
       </c>
       <c r="G290" t="n">
@@ -37914,7 +37914,7 @@
       </c>
       <c r="C291" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Portugal Liga 3</t>
         </is>
       </c>
       <c r="D291" t="inlineStr">
@@ -37924,12 +37924,12 @@
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Fortuna Sittard</t>
+          <t>Paredes</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
         <is>
-          <t>Heerenveen</t>
+          <t>Sporting Braga II</t>
         </is>
       </c>
       <c r="G291" t="n">
@@ -37950,13 +37950,13 @@
         </is>
       </c>
       <c r="L291" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="M291" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="N291" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="O291" t="n">
         <v>0</v>
@@ -37989,10 +37989,10 @@
         <v>0</v>
       </c>
       <c r="Y291" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Z291" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="AA291" t="n">
         <v>0</v>
@@ -38043,7 +38043,7 @@
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -38053,12 +38053,12 @@
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>KV Kortrijk</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="G292" t="n">
@@ -38172,7 +38172,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Algeria Ligue 1</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -38182,12 +38182,12 @@
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
         <is>
-          <t>Lokeren-Temse</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="G293" t="n">
@@ -38301,22 +38301,22 @@
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>Club Brugge II</t>
+          <t>Novorizontino</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>Lierse Kempenzonen</t>
+          <t>Remo</t>
         </is>
       </c>
       <c r="G294" t="n">
@@ -38430,22 +38430,22 @@
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>2025</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
         <is>
-          <t>Novorizontino</t>
+          <t>Club Brugge II</t>
         </is>
       </c>
       <c r="F295" t="inlineStr">
         <is>
-          <t>Remo</t>
+          <t>Lierse Kempenzonen</t>
         </is>
       </c>
       <c r="G295" t="n">
@@ -38559,22 +38559,22 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Algeria Ligue 1</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2025</t>
         </is>
       </c>
       <c r="E296" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>Sport Recife</t>
         </is>
       </c>
       <c r="F296" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Atlético Mineiro</t>
         </is>
       </c>
       <c r="G296" t="n">
@@ -39333,7 +39333,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -39343,12 +39343,12 @@
       </c>
       <c r="E302" t="inlineStr">
         <is>
-          <t>PEC Zwolle</t>
+          <t>Real Murcia</t>
         </is>
       </c>
       <c r="F302" t="inlineStr">
         <is>
-          <t>Sparta Rotterdam</t>
+          <t>Gimnàstic de Tarragona</t>
         </is>
       </c>
       <c r="G302" t="n">
@@ -39369,13 +39369,13 @@
         </is>
       </c>
       <c r="L302" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="M302" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N302" t="n">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="O302" t="n">
         <v>0</v>
@@ -39408,10 +39408,10 @@
         <v>0</v>
       </c>
       <c r="Y302" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="Z302" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AA302" t="n">
         <v>0</v>
@@ -39462,7 +39462,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -39472,12 +39472,12 @@
       </c>
       <c r="E303" t="inlineStr">
         <is>
-          <t>Real Murcia</t>
+          <t>PEC Zwolle</t>
         </is>
       </c>
       <c r="F303" t="inlineStr">
         <is>
-          <t>Gimnàstic de Tarragona</t>
+          <t>Sparta Rotterdam</t>
         </is>
       </c>
       <c r="G303" t="n">
@@ -39498,13 +39498,13 @@
         </is>
       </c>
       <c r="L303" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="M303" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N303" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="O303" t="n">
         <v>0</v>
@@ -39537,10 +39537,10 @@
         <v>0</v>
       </c>
       <c r="Y303" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="Z303" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AA303" t="n">
         <v>0</v>
@@ -39591,7 +39591,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Spain Primera Division RFEF Group 2</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -39601,12 +39601,12 @@
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>RCD Espanyol</t>
+          <t>Arenas de Getxo</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Osasuna II</t>
         </is>
       </c>
       <c r="G304" t="n">
@@ -39627,13 +39627,13 @@
         </is>
       </c>
       <c r="L304" t="n">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="M304" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="N304" t="n">
-        <v>2.33</v>
+        <v>0</v>
       </c>
       <c r="O304" t="n">
         <v>0</v>
@@ -39666,10 +39666,10 @@
         <v>0</v>
       </c>
       <c r="Y304" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="Z304" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AA304" t="n">
         <v>0</v>
@@ -39720,7 +39720,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Spain Primera Division RFEF Group 2</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -39730,12 +39730,12 @@
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>Arenas de Getxo</t>
+          <t>Málaga CF</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
         <is>
-          <t>Osasuna II</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="G305" t="n">
@@ -39849,7 +39849,7 @@
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -39859,12 +39859,12 @@
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>Málaga CF</t>
+          <t>RCD Espanyol</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
         <is>
-          <t>Córdoba</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="G306" t="n">
@@ -39885,13 +39885,13 @@
         </is>
       </c>
       <c r="L306" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="M306" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N306" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="O306" t="n">
         <v>0</v>
@@ -39924,10 +39924,10 @@
         <v>0</v>
       </c>
       <c r="Y306" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="Z306" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AA306" t="n">
         <v>0</v>
@@ -40623,7 +40623,7 @@
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Brazil Serie A</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -40633,12 +40633,12 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Atlético PR</t>
+          <t>Internacional</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
         <is>
-          <t>Volta Redonda</t>
+          <t>Bahia</t>
         </is>
       </c>
       <c r="G312" t="n">
@@ -40752,7 +40752,7 @@
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Brazil Serie A</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -40762,12 +40762,12 @@
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>Internacional</t>
+          <t>Atlético PR</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
         <is>
-          <t>Bahia</t>
+          <t>Volta Redonda</t>
         </is>
       </c>
       <c r="G313" t="n">
@@ -40881,7 +40881,7 @@
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Brazil Serie B</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
@@ -40891,12 +40891,12 @@
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Vila Nova</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Avaí</t>
         </is>
       </c>
       <c r="G314" t="n">
@@ -41010,7 +41010,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Brazil Serie B</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -41020,12 +41020,12 @@
       </c>
       <c r="E315" t="inlineStr">
         <is>
-          <t>Vila Nova</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="F315" t="inlineStr">
         <is>
-          <t>Avaí</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G315" t="n">
